--- a/reports.xlsx
+++ b/reports.xlsx
@@ -19,31 +19,31 @@
     <t>Reports</t>
   </si>
   <si>
-    <t>We conducted an examination of the latest sales data and addressed several key issues, taking a close look at finding solutions to existing problems and mitigating potential security threats that could impact our relationship management strategies.</t>
+    <t>We maked exam of the lasts data of sells and addressed many keys issues, putting a strong look in find solutions for the problems that exist and mitigationing potentials threats of security that can impactating our strategies of relationship management.</t>
   </si>
   <si>
-    <t>Iso/IEC 38500 is a standard designed to drive efficient and effective IT governance, providing a framework that enables organizations to establish dependable and trustworthy IT systems. At its core, this standard aims to inspire stakeholder confidence in a company's IT infrastructure, assuring them of its robustness and reliability. By embracing Iso/IEC 38500, organizations can safeguard the security and integrity of their operations, cultivating a culture of trust and reliability that extends to their stakeholders and reinforces their reputation.</t>
+    <t>Delving into the realm of Iso/IEC 38500, a standard crafted to promote efficient and effective IT governance, we find a framework that fosters dependable and trustworthy IT systems within organizations. The primary objective of this standard is to instill confidence among stakeholders that a company's IT infrastructure is robust and reliable. By adopting Iso/IEC 38500, businesses can ensure the security and integrity of their operations, ultimately nurturing a culture of trust and reliability that resonates with their stakeholders and reinforces their reputation.</t>
   </si>
   <si>
-    <t>Within the Iso/IEC 38500 framework, a standard designed to facilitate efficient and effective governance of Information Technology (IT), lies a structured approach that cultivates dependable and trustworthy IT systems within organizations. The primary goal of this standard is to establish confidence among stakeholders that a company's IT infrastructure is robust and reliable. By embracing Iso/IEC 38500, businesses can ensure the security and integrity of their operations, ultimately fostering a culture of trust and reliability that resonates with stakeholders and enhances their reputation.</t>
+    <t>Delving inside the realm of the Iso/IEC 38500, a standard crafted for to promote the efficient and effective governance of TI, we finds a framework that fosters systems of TI dependables and trustworthies inside the organizations. The primary objective of this pattern is to put confidence between the stakeholders that the infrastructure of TI of a company is robust and reliable. By adopting Iso/IEC 38500, the businesses can assure the security and integrity of their operations, ultimately nurturing a culture of trust and reliability that makes noise with their stakeholders and fixes their reputation.</t>
   </si>
   <si>
-    <t>This morning, we kicked off the workday with a team meeting to review our individual roles and the separate initiatives we've been working on. We took a step back to assess our overall approach, ensuring it aligns with our objectives and identifying areas for improvement to meet all the necessary requirements.</t>
+    <t>This morning, we gave a kick off in the day of work with a meeting of team for to review our roles individuals and the initiatives we have been working separately. We tooked a step to back for to evaluate our approach overall, making sure it stays in the track with our objectives and pinpointing areas where we can improve for to meet all the patterns requireds.</t>
   </si>
   <si>
-    <t>We recently conducted an in-depth examination of our sales data and addressed various key issues, placing a strong emphasis on finding solutions to existing problems and mitigating potential safety threats that could impact our relationship management strategies.</t>
+    <t>We was examining the data of sells more lates and made the addressment of various issues-key, placing one force emphasis in find solutions for problems that already exists and making the mitigation of potential threats of safety that could impacting our strategies of management of relationship.</t>
   </si>
   <si>
-    <t>We are gathering today to set key objectives that align with the company's budget and to clarify expectations surrounding IT governance.</t>
+    <t>We are coming all together today for to establish objectives-keys that makes alignment with the budget of the company and for to make clear the expectations around the Governance of TI.</t>
   </si>
   <si>
-    <t>Our next meeting is set for the week after next.</t>
+    <t>We're scheduled to meet again the week after next.</t>
   </si>
   <si>
-    <t>Today, we gather to assess the key roles and specialized expertise of our management team. As we strive for excellence, it's clear that seamless collaboration and thoughtful task allocation are crucial in driving our organization forward and staying true to its core objectives. By working together in harmony, we can foster a unified and thriving work environment where everyone pulls together to achieve common goals and celebrate shared success.</t>
+    <t>We've come together today to examine the core responsibilities of our management team, focusing on their unique areas of specialization. It has become evident that effective collaboration and strategic task distribution are essential in aligning our organization with its primary goals and priorities, ultimately cultivating a cohesive and successful work environment that thrives on unity and collective achievement.</t>
   </si>
   <si>
-    <t>We have gathered to assess the key roles and specialties within our management team, aiming to optimize our collective performance. It has become clear that seamless collaboration and the strategic delegation of tasks are crucial in ensuring our organization remains focused on its core objectives, thereby fostering a unified and productive work environment that celebrates teamwork and shared success. Our next meeting will concentrate on addressing compliance concerns and reviewing the latest ISO standards, enabling us to stay current and adhere to the highest industry benchmarks.</t>
+    <t>We've come together today to examine the core responsibilities of our management team, focusing on their unique areas of specialization. It has become evident that effective collaboration and strategic task distribution are essential in aligning our organization with its primary goals and priorities, ultimately cultivating a cohesive and successful work environment that thrives on unity and collective achievement.Our upcoming meeting will focus on tackling compliance issues and examining the most recent ISO standards, allowing us to stay up-to-date and aligned with industry best practices.</t>
   </si>
   <si>
     <t>=B</t>
@@ -496,7 +496,7 @@
       </c>
       <c r="C2" s="6" t="str">
         <f>IF("We maked exam of the lasts data of sells and addressed many keys issues, putting a strong look in find solutions for the problems that exist and mitigationing potentials threats of security that can impactating our strategies of relationship management."&lt;&gt;B2,"√","")</f>
-        <v>√</v>
+        <v/>
       </c>
       <c r="D2" s="7" t="str">
         <f t="shared" ref="D2:D10" si="1">IF(C2&lt;&gt;C2,"✔","")</f>
@@ -520,7 +520,7 @@
       </c>
       <c r="C3" s="6" t="str">
         <f>IF("Delving into the realm of Iso/IEC 38500, a standard crafted to promote efficient and effective IT governance, we find a framework that fosters dependable and trustworthy IT systems within organizations. The primary objective of this standard is to instill"&amp;" confidence among stakeholders that a company's IT infrastructure is robust and reliable. By adopting Iso/IEC 38500, businesses can ensure the security and integrity of their operations, ultimately nurturing a culture of trust and reliability that resonat"&amp;"es with their stakeholders and reinforces their reputation."&lt;&gt;B3,"√","")</f>
-        <v>√</v>
+        <v/>
       </c>
       <c r="D3" s="7" t="str">
         <f t="shared" si="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="C4" s="6" t="str">
         <f>IF("Delving inside the realm of the Iso/IEC 38500, a standard crafted for to promote the efficient and effective governance of TI, we finds a framework that fosters systems of TI dependables and trustworthies inside the organizations. The primary objective of"&amp;" this pattern is to put confidence between the stakeholders that the infrastructure of TI of a company is robust and reliable. By adopting Iso/IEC 38500, the businesses can assure the security and integrity of their operations, ultimately nurturing a cult"&amp;"ure of trust and reliability that makes noise with their stakeholders and fixes their reputation."&lt;&gt;B4,"√","")</f>
-        <v>√</v>
+        <v/>
       </c>
       <c r="D4" s="7" t="str">
         <f t="shared" si="1"/>
@@ -568,7 +568,7 @@
       </c>
       <c r="C5" s="6" t="str">
         <f>IF("This morning, we gave a kick off in the day of work with a meeting of team for to review our roles individuals and the initiatives we have been working separately. We tooked a step to back for to evaluate our approach overall, making sure it stays in the "&amp;"track with our objectives and pinpointing areas where we can improve for to meet all the patterns requireds."&lt;&gt;B5,"√","")</f>
-        <v>√</v>
+        <v/>
       </c>
       <c r="D5" s="7" t="str">
         <f t="shared" si="1"/>
@@ -592,7 +592,7 @@
       </c>
       <c r="C6" s="6" t="str">
         <f>IF("We was examining the data of sells more lates and made the addressment of various issues-key, placing one force emphasis in find solutions for problems that already exists and making the mitigation of potential threats of safety that could impacting our s"&amp;"trategies of management of relationship."&lt;&gt;B6,"√","")</f>
-        <v>√</v>
+        <v/>
       </c>
       <c r="D6" s="7" t="str">
         <f t="shared" si="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="C7" s="6" t="str">
         <f>IF("We are coming all together today for to establish objectives-keys that makes alignment with the budget of the company and for to make clear the expectations around the Governance of TI."&lt;&gt;B7,"√","")</f>
-        <v>√</v>
+        <v/>
       </c>
       <c r="D7" s="7" t="str">
         <f t="shared" si="1"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C8" s="6" t="str">
         <f>IF("We're scheduled to meet again the week after next."&lt;&gt;B8,"√","")</f>
-        <v>√</v>
+        <v/>
       </c>
       <c r="D8" s="7" t="str">
         <f t="shared" si="1"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="C9" s="6" t="str">
         <f>IF("We've come together today to examine the core responsibilities of our management team, focusing on their unique areas of specialization. It has become evident that effective collaboration and strategic task distribution are essential in aligning our organ"&amp;"ization with its primary goals and priorities, ultimately cultivating a cohesive and successful work environment that thrives on unity and collective achievement."&lt;&gt;B9,"√","")</f>
-        <v>√</v>
+        <v/>
       </c>
       <c r="D9" s="7" t="str">
         <f t="shared" si="1"/>
@@ -688,7 +688,7 @@
       </c>
       <c r="C10" s="6" t="str">
         <f>IF("We've come together today to examine the core responsibilities of our management team, focusing on their unique areas of specialization. It has become evident that effective collaboration and strategic task distribution are essential in aligning our organ"&amp;"ization with its primary goals and priorities, ultimately cultivating a cohesive and successful work environment that thrives on unity and collective achievement.Our upcoming meeting will focus on tackling compliance issues and examining the most recent I"&amp;"SO standards, allowing us to stay up-to-date and aligned with industry best practices."&lt;&gt;B10,"√","")</f>
-        <v>√</v>
+        <v/>
       </c>
       <c r="D10" s="7" t="str">
         <f t="shared" si="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="B12" s="17" t="str">
         <f>IF(B10&lt;&gt;"We've come together today to examine the core responsibilities of our management team, focusing on their unique areas of specialization. It has become evident that effective collaboration and strategic task distribution are essential in aligning our organ"&amp;"ization with its primary goals and priorities, ultimately cultivating a cohesive and successful work environment that thrives on unity and collective achievement.Our upcoming meeting will focus on tackling compliance issues and examining the most recent I"&amp;"SO standards, allowing us to stay up-to-date and aligned with industry best practices.","complete service","")</f>
-        <v>complete service</v>
+        <v/>
       </c>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
